--- a/ProductionBuild/financials.result.xlsx
+++ b/ProductionBuild/financials.result.xlsx
@@ -439,10 +439,10 @@
         <v>16.47999954223633</v>
       </c>
       <c r="F3">
-        <v>45.83000183105469</v>
+        <v>45.58000183105469</v>
       </c>
       <c r="G3">
-        <v>29.35000228881836</v>
+        <v>29.10000228881836</v>
       </c>
     </row>
     <row r="4">
@@ -466,10 +466,10 @@
         <v>21.84000015258789</v>
       </c>
       <c r="F4">
-        <v>26.39999961853027</v>
+        <v>26.13999938964844</v>
       </c>
       <c r="G4">
-        <v>4.559999465942383</v>
+        <v>4.299999237060547</v>
       </c>
     </row>
     <row r="5">
@@ -493,10 +493,10 @@
         <v>16.48999977111816</v>
       </c>
       <c r="F5">
-        <v>18.95999908447266</v>
+        <v>19.10000038146973</v>
       </c>
       <c r="G5">
-        <v>2.469999313354492</v>
+        <v>2.610000610351563</v>
       </c>
     </row>
     <row r="6">
@@ -520,10 +520,10 @@
         <v>35.7400016784668</v>
       </c>
       <c r="F6">
-        <v>37.56000137329102</v>
+        <v>37.22000122070313</v>
       </c>
       <c r="G6">
-        <v>1.819999694824219</v>
+        <v>1.479999542236328</v>
       </c>
     </row>
     <row r="7">
@@ -547,10 +547,10 @@
         <v>15.53947353363037</v>
       </c>
       <c r="F7">
-        <v>17.19000053405762</v>
+        <v>17.22999954223633</v>
       </c>
       <c r="G7">
-        <v>1.650527000427246</v>
+        <v>1.690526008605957</v>
       </c>
     </row>
     <row r="8">
@@ -574,10 +574,10 @@
         <v>25.20000076293945</v>
       </c>
       <c r="F8">
-        <v>49.31000137329102</v>
+        <v>48.45999908447266</v>
       </c>
       <c r="G8">
-        <v>24.11000061035156</v>
+        <v>23.2599983215332</v>
       </c>
     </row>
     <row r="9">
@@ -601,10 +601,10 @@
         <v>6.769999980926514</v>
       </c>
       <c r="F9">
-        <v>22.46999931335449</v>
+        <v>22.29000091552734</v>
       </c>
       <c r="G9">
-        <v>15.69999933242798</v>
+        <v>15.52000093460083</v>
       </c>
     </row>
     <row r="10">
@@ -628,10 +628,10 @@
         <v>23.48333358764648</v>
       </c>
       <c r="F10">
-        <v>39.20000076293945</v>
+        <v>38.47000122070313</v>
       </c>
       <c r="G10">
-        <v>15.71666717529297</v>
+        <v>14.98666763305664</v>
       </c>
     </row>
     <row r="11">
@@ -655,10 +655,10 @@
         <v>39.58000183105469</v>
       </c>
       <c r="F11">
-        <v>27.23999977111816</v>
+        <v>27.48999977111816</v>
       </c>
       <c r="G11">
-        <v>-12.34000205993652</v>
+        <v>-12.09000205993652</v>
       </c>
     </row>
     <row r="12">
@@ -682,10 +682,10 @@
         <v>31.85000038146973</v>
       </c>
       <c r="F12">
-        <v>53.41999816894531</v>
+        <v>53.02999877929688</v>
       </c>
       <c r="G12">
-        <v>21.56999778747559</v>
+        <v>21.17999839782715</v>
       </c>
     </row>
     <row r="13">
@@ -709,10 +709,10 @@
         <v>55.68000030517578</v>
       </c>
       <c r="F13">
-        <v>75.87000274658203</v>
+        <v>75.13999938964844</v>
       </c>
       <c r="G13">
-        <v>20.19000244140625</v>
+        <v>19.45999908447266</v>
       </c>
     </row>
     <row r="14">
@@ -736,10 +736,10 @@
         <v>21.8700008392334</v>
       </c>
       <c r="F14">
-        <v>34.15999984741211</v>
+        <v>33.59999847412109</v>
       </c>
       <c r="G14">
-        <v>12.28999900817871</v>
+        <v>11.7299976348877</v>
       </c>
     </row>
     <row r="15">
@@ -760,7 +760,7 @@
         <v>13.31</v>
       </c>
       <c r="F15">
-        <v>24.17000007629395</v>
+        <v>24.14999961853027</v>
       </c>
     </row>
     <row r="16">
@@ -784,10 +784,10 @@
         <v>36.68000030517578</v>
       </c>
       <c r="F16">
-        <v>73.20999908447266</v>
+        <v>73.56999969482422</v>
       </c>
       <c r="G16">
-        <v>36.52999877929688</v>
+        <v>36.88999938964844</v>
       </c>
     </row>
     <row r="17">
@@ -811,10 +811,10 @@
         <v>41.5</v>
       </c>
       <c r="F17">
-        <v>48.16999816894531</v>
+        <v>48.06000137329102</v>
       </c>
       <c r="G17">
-        <v>6.669998168945313</v>
+        <v>6.560001373291016</v>
       </c>
     </row>
     <row r="18">
@@ -838,10 +838,10 @@
         <v>44.68000030517578</v>
       </c>
       <c r="F18">
-        <v>29.09000015258789</v>
+        <v>29</v>
       </c>
       <c r="G18">
-        <v>-15.59000015258789</v>
+        <v>-15.68000030517578</v>
       </c>
     </row>
     <row r="19">
@@ -865,10 +865,10 @@
         <v>43.40909194946289</v>
       </c>
       <c r="F19">
-        <v>179.1499938964844</v>
+        <v>178.3999938964844</v>
       </c>
       <c r="G19">
-        <v>135.7409019470215</v>
+        <v>134.9909019470215</v>
       </c>
     </row>
     <row r="20">
@@ -892,10 +892,10 @@
         <v>15.18000030517578</v>
       </c>
       <c r="F20">
-        <v>25.79999923706055</v>
+        <v>25.70000076293945</v>
       </c>
       <c r="G20">
-        <v>10.61999893188477</v>
+        <v>10.52000045776367</v>
       </c>
     </row>
     <row r="21">
@@ -919,10 +919,10 @@
         <v>22.73556709289551</v>
       </c>
       <c r="F21">
-        <v>50.68000030517578</v>
+        <v>50.63000106811523</v>
       </c>
       <c r="G21">
-        <v>27.94443321228027</v>
+        <v>27.89443397521973</v>
       </c>
     </row>
     <row r="22">
@@ -946,10 +946,10 @@
         <v>13.22000026702881</v>
       </c>
       <c r="F22">
-        <v>16.96999931335449</v>
+        <v>16.81999969482422</v>
       </c>
       <c r="G22">
-        <v>3.749999046325684</v>
+        <v>3.59999942779541</v>
       </c>
     </row>
     <row r="23">
@@ -973,10 +973,10 @@
         <v>40.18000030517578</v>
       </c>
       <c r="F23">
-        <v>90.63999938964844</v>
+        <v>90.47000122070313</v>
       </c>
       <c r="G23">
-        <v>50.45999908447266</v>
+        <v>50.29000091552734</v>
       </c>
     </row>
     <row r="24">
@@ -1000,10 +1000,10 @@
         <v>14.10000038146973</v>
       </c>
       <c r="F24">
-        <v>28.48999977111816</v>
+        <v>28.07999992370605</v>
       </c>
       <c r="G24">
-        <v>14.38999938964844</v>
+        <v>13.97999954223633</v>
       </c>
     </row>
     <row r="25">
@@ -1027,10 +1027,10 @@
         <v>15.22999954223633</v>
       </c>
       <c r="F25">
-        <v>40.72999954223633</v>
+        <v>40.31999969482422</v>
       </c>
       <c r="G25">
-        <v>25.5</v>
+        <v>25.09000015258789</v>
       </c>
     </row>
     <row r="26">
@@ -1054,10 +1054,10 @@
         <v>20.81229782104492</v>
       </c>
       <c r="F26">
-        <v>47.61999893188477</v>
+        <v>47.0099983215332</v>
       </c>
       <c r="G26">
-        <v>26.80770111083984</v>
+        <v>26.19770050048828</v>
       </c>
     </row>
     <row r="27">
@@ -1081,10 +1081,10 @@
         <v>18.27000045776367</v>
       </c>
       <c r="F27">
-        <v>22.10000038146973</v>
+        <v>22.04000091552734</v>
       </c>
       <c r="G27">
-        <v>3.829999923706055</v>
+        <v>3.770000457763672</v>
       </c>
     </row>
     <row r="28">
@@ -1108,10 +1108,10 @@
         <v>41.09000015258789</v>
       </c>
       <c r="F28">
-        <v>48.72000122070313</v>
+        <v>47.40999984741211</v>
       </c>
       <c r="G28">
-        <v>7.630001068115234</v>
+        <v>6.319999694824219</v>
       </c>
     </row>
     <row r="29">
@@ -1135,10 +1135,10 @@
         <v>66.26999664306641</v>
       </c>
       <c r="F29">
-        <v>36.68999862670898</v>
+        <v>36.83000183105469</v>
       </c>
       <c r="G29">
-        <v>-29.57999801635742</v>
+        <v>-29.43999481201172</v>
       </c>
     </row>
     <row r="30">
@@ -1162,10 +1162,10 @@
         <v>36.77000045776367</v>
       </c>
       <c r="F30">
-        <v>54.04999923706055</v>
+        <v>54.65000152587891</v>
       </c>
       <c r="G30">
-        <v>17.27999877929688</v>
+        <v>17.88000106811523</v>
       </c>
     </row>
     <row r="31">
@@ -1189,10 +1189,10 @@
         <v>33.90000152587891</v>
       </c>
       <c r="F31">
-        <v>68.73999786376953</v>
+        <v>67.16999816894531</v>
       </c>
       <c r="G31">
-        <v>34.83999633789063</v>
+        <v>33.26999664306641</v>
       </c>
     </row>
     <row r="32">
@@ -1216,10 +1216,10 @@
         <v>17.81999969482422</v>
       </c>
       <c r="F32">
-        <v>38.22999954223633</v>
+        <v>38.31000137329102</v>
       </c>
       <c r="G32">
-        <v>20.40999984741211</v>
+        <v>20.4900016784668</v>
       </c>
     </row>
     <row r="33">
@@ -1243,10 +1243,10 @@
         <v>39.88000106811523</v>
       </c>
       <c r="F33">
-        <v>22.60000038146973</v>
+        <v>22.6299991607666</v>
       </c>
       <c r="G33">
-        <v>-17.28000068664551</v>
+        <v>-17.25000190734863</v>
       </c>
     </row>
     <row r="34">
@@ -1270,10 +1270,10 @@
         <v>5.959052085876465</v>
       </c>
       <c r="F34">
-        <v>16.11000061035156</v>
+        <v>15.97000026702881</v>
       </c>
       <c r="G34">
-        <v>10.1509485244751</v>
+        <v>10.01094818115234</v>
       </c>
     </row>
     <row r="35">
@@ -1297,10 +1297,10 @@
         <v>22.13999938964844</v>
       </c>
       <c r="F35">
-        <v>58.90999984741211</v>
+        <v>59.70999908447266</v>
       </c>
       <c r="G35">
-        <v>36.77000045776367</v>
+        <v>37.56999969482422</v>
       </c>
     </row>
     <row r="36">
@@ -1324,10 +1324,10 @@
         <v>52.59000015258789</v>
       </c>
       <c r="F36">
-        <v>48.52000045776367</v>
+        <v>47.52000045776367</v>
       </c>
       <c r="G36">
-        <v>-4.069999694824219</v>
+        <v>-5.069999694824219</v>
       </c>
     </row>
     <row r="37">
@@ -1351,10 +1351,10 @@
         <v>104.0599975585938</v>
       </c>
       <c r="F37">
-        <v>96.44999694824219</v>
+        <v>94.84999847412109</v>
       </c>
       <c r="G37">
-        <v>-7.610000610351563</v>
+        <v>-9.209999084472656</v>
       </c>
     </row>
     <row r="38">
@@ -1378,10 +1378,10 @@
         <v>14.35999965667725</v>
       </c>
       <c r="F38">
-        <v>28.35000038146973</v>
+        <v>28.20999908447266</v>
       </c>
       <c r="G38">
-        <v>13.99000072479248</v>
+        <v>13.84999942779541</v>
       </c>
     </row>
     <row r="39">
@@ -1405,10 +1405,10 @@
         <v>38.40999984741211</v>
       </c>
       <c r="F39">
-        <v>70.31999969482422</v>
+        <v>70.48000335693359</v>
       </c>
       <c r="G39">
-        <v>31.90999984741211</v>
+        <v>32.07000350952148</v>
       </c>
     </row>
     <row r="40">
@@ -1432,10 +1432,10 @@
         <v>23.76000022888184</v>
       </c>
       <c r="F40">
-        <v>42.16999816894531</v>
+        <v>41.7400016784668</v>
       </c>
       <c r="G40">
-        <v>18.40999794006348</v>
+        <v>17.98000144958496</v>
       </c>
     </row>
     <row r="41">
@@ -1486,10 +1486,10 @@
         <v>24.14999961853027</v>
       </c>
       <c r="F42">
-        <v>35.5099983215332</v>
+        <v>35.63999938964844</v>
       </c>
       <c r="G42">
-        <v>11.35999870300293</v>
+        <v>11.48999977111816</v>
       </c>
     </row>
     <row r="43">
@@ -1513,10 +1513,10 @@
         <v>47.02000045776367</v>
       </c>
       <c r="F43">
-        <v>51.06999969482422</v>
+        <v>50.95000076293945</v>
       </c>
       <c r="G43">
-        <v>4.049999237060547</v>
+        <v>3.930000305175781</v>
       </c>
     </row>
     <row r="44">
@@ -1540,10 +1540,10 @@
         <v>75.26000213623047</v>
       </c>
       <c r="F44">
-        <v>99.13999938964844</v>
+        <v>100.2399978637695</v>
       </c>
       <c r="G44">
-        <v>23.87999725341797</v>
+        <v>24.97999572753906</v>
       </c>
     </row>
     <row r="45">
@@ -1567,10 +1567,10 @@
         <v>28.13999938964844</v>
       </c>
       <c r="F45">
-        <v>57.18000030517578</v>
+        <v>57.79999923706055</v>
       </c>
       <c r="G45">
-        <v>29.04000091552734</v>
+        <v>29.65999984741211</v>
       </c>
     </row>
     <row r="46">
@@ -1594,10 +1594,10 @@
         <v>51.36999893188477</v>
       </c>
       <c r="F46">
-        <v>56.84000015258789</v>
+        <v>56.59999847412109</v>
       </c>
       <c r="G46">
-        <v>5.470001220703125</v>
+        <v>5.229999542236328</v>
       </c>
     </row>
     <row r="47">
@@ -1621,10 +1621,10 @@
         <v>32</v>
       </c>
       <c r="F47">
-        <v>71.59999847412109</v>
+        <v>71.79000091552734</v>
       </c>
       <c r="G47">
-        <v>39.59999847412109</v>
+        <v>39.79000091552734</v>
       </c>
     </row>
   </sheetData>

--- a/ProductionBuild/financials.result.xlsx
+++ b/ProductionBuild/financials.result.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G47"/>
+  <dimension ref="A1:P47"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -367,859 +367,1871 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>sector</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
           <t>avgdividend</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>totaldividends</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>price_start</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>price_end</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>change</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>totalreturn</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>totalreturnover10</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>shares500</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>totalspend</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>fiveyearequityproj</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>fiveyeardivproj</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>totalfiveyearview</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>selected</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Absa Group Ltd</t>
+          <t>DBS Group Holdings Ltd</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>AGRPY</t>
-        </is>
-      </c>
-      <c r="C2">
-        <v>1.1849</v>
+          <t>DBSDY</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>financials</t>
+        </is>
       </c>
       <c r="D2">
-        <v>11.849</v>
+        <v>3.441421636363637</v>
       </c>
       <c r="E2">
-        <v>25</v>
+        <v>37.855638</v>
       </c>
       <c r="F2">
-        <v>30.45000076293945</v>
+        <v>43.40909194946289</v>
       </c>
       <c r="G2">
-        <v>5.450000762939453</v>
+        <v>178.4900054931641</v>
+      </c>
+      <c r="H2">
+        <v>135.0809135437012</v>
+      </c>
+      <c r="I2">
+        <v>172.9365515437012</v>
+      </c>
+      <c r="J2">
+        <v>17.29365515437012</v>
+      </c>
+      <c r="K2">
+        <v>3</v>
+      </c>
+      <c r="L2">
+        <v>535.4700164794922</v>
+      </c>
+      <c r="M2">
+        <v>86.46827577185059</v>
+      </c>
+      <c r="N2">
+        <v>17.20710818181818</v>
+      </c>
+      <c r="O2">
+        <v>103.6753839536688</v>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Allianz SE</t>
+          <t>HSBC Holdings PLC</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>ALIZY</t>
-        </is>
-      </c>
-      <c r="C3">
-        <v>1.1421</v>
+          <t>HSBC</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>financials</t>
+        </is>
       </c>
       <c r="D3">
-        <v>11.421</v>
+        <v>2.268181818181818</v>
       </c>
       <c r="E3">
-        <v>16.47999954223633</v>
+        <v>24.95</v>
       </c>
       <c r="F3">
-        <v>45.58000183105469</v>
+        <v>40.18000030517578</v>
       </c>
       <c r="G3">
-        <v>29.10000228881836</v>
+        <v>89.63999938964844</v>
+      </c>
+      <c r="H3">
+        <v>49.45999908447266</v>
+      </c>
+      <c r="I3">
+        <v>74.40999908447266</v>
+      </c>
+      <c r="J3">
+        <v>7.440999908447266</v>
+      </c>
+      <c r="K3">
+        <v>6</v>
+      </c>
+      <c r="L3">
+        <v>537.8399963378906</v>
+      </c>
+      <c r="M3">
+        <v>37.20499954223633</v>
+      </c>
+      <c r="N3">
+        <v>11.34090909090909</v>
+      </c>
+      <c r="O3">
+        <v>48.54590863314542</v>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>ANZ Group Holdings Limited</t>
+          <t>OneMain Holdings Inc</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>ANZGY</t>
-        </is>
-      </c>
-      <c r="C4">
-        <v>0.9964000000000001</v>
+          <t>OMF</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>financials</t>
+        </is>
       </c>
       <c r="D4">
-        <v>9.964</v>
+        <v>4.45375</v>
       </c>
       <c r="E4">
-        <v>21.84000015258789</v>
+        <v>35.63</v>
       </c>
       <c r="F4">
-        <v>26.13999938964844</v>
+        <v>22.13999938964844</v>
       </c>
       <c r="G4">
-        <v>4.299999237060547</v>
+        <v>59</v>
+      </c>
+      <c r="H4">
+        <v>36.86000061035156</v>
+      </c>
+      <c r="I4">
+        <v>72.49000061035156</v>
+      </c>
+      <c r="J4">
+        <v>7.249000061035156</v>
+      </c>
+      <c r="K4">
+        <v>9</v>
+      </c>
+      <c r="L4">
+        <v>531</v>
+      </c>
+      <c r="M4">
+        <v>36.24500030517578</v>
+      </c>
+      <c r="N4">
+        <v>22.26875</v>
+      </c>
+      <c r="O4">
+        <v>58.51375030517578</v>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>ARES CAPITAL CORPORATION</t>
+          <t>Moelis &amp; Co</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>ARCC</t>
-        </is>
-      </c>
-      <c r="C5">
-        <v>1.564545454545454</v>
+          <t>MC</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>financials</t>
+        </is>
       </c>
       <c r="D5">
-        <v>17.21</v>
+        <v>3.109363636363637</v>
       </c>
       <c r="E5">
-        <v>16.48999977111816</v>
+        <v>34.203</v>
       </c>
       <c r="F5">
-        <v>19.10000038146973</v>
+        <v>33.90000152587891</v>
       </c>
       <c r="G5">
-        <v>2.610000610351563</v>
+        <v>67.23999786376953</v>
+      </c>
+      <c r="H5">
+        <v>33.33999633789063</v>
+      </c>
+      <c r="I5">
+        <v>67.54299633789063</v>
+      </c>
+      <c r="J5">
+        <v>6.754299633789063</v>
+      </c>
+      <c r="K5">
+        <v>8</v>
+      </c>
+      <c r="L5">
+        <v>537.9199829101563</v>
+      </c>
+      <c r="M5">
+        <v>33.77149816894531</v>
+      </c>
+      <c r="N5">
+        <v>15.54681818181818</v>
+      </c>
+      <c r="O5">
+        <v>49.3183163507635</v>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Atlantic Union Bankshares Corp</t>
+          <t>T. Rowe Price Group Inc</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>AUB</t>
-        </is>
-      </c>
-      <c r="C6">
-        <v>0.9781818181818183</v>
+          <t>TROW</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>financials</t>
+        </is>
       </c>
       <c r="D6">
-        <v>10.76</v>
+        <v>3.789090909090909</v>
       </c>
       <c r="E6">
-        <v>35.7400016784668</v>
+        <v>41.68</v>
       </c>
       <c r="F6">
-        <v>37.22000122070313</v>
+        <v>75.26000213623047</v>
       </c>
       <c r="G6">
-        <v>1.479999542236328</v>
+        <v>99.48999786376953</v>
+      </c>
+      <c r="H6">
+        <v>24.22999572753906</v>
+      </c>
+      <c r="I6">
+        <v>65.90999572753907</v>
+      </c>
+      <c r="J6">
+        <v>6.590999572753907</v>
+      </c>
+      <c r="K6">
+        <v>6</v>
+      </c>
+      <c r="L6">
+        <v>596.9399871826172</v>
+      </c>
+      <c r="M6">
+        <v>32.95499786376953</v>
+      </c>
+      <c r="N6">
+        <v>18.94545454545455</v>
+      </c>
+      <c r="O6">
+        <v>51.90045240922408</v>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Aviva PLC</t>
+          <t>Grupo Cibest S.A</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>AVVIY</t>
-        </is>
-      </c>
-      <c r="C7">
-        <v>0.9795454545454545</v>
+          <t>CIB</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>financials</t>
+        </is>
       </c>
       <c r="D7">
-        <v>10.775</v>
+        <v>2.433545454545455</v>
       </c>
       <c r="E7">
-        <v>15.53947353363037</v>
+        <v>26.769</v>
       </c>
       <c r="F7">
-        <v>17.22999954223633</v>
+        <v>36.68000030517578</v>
       </c>
       <c r="G7">
-        <v>1.690526008605957</v>
+        <v>71.88999938964844</v>
+      </c>
+      <c r="H7">
+        <v>35.20999908447266</v>
+      </c>
+      <c r="I7">
+        <v>61.97899908447266</v>
+      </c>
+      <c r="J7">
+        <v>6.197899908447266</v>
+      </c>
+      <c r="K7">
+        <v>7</v>
+      </c>
+      <c r="L7">
+        <v>503.2299957275391</v>
+      </c>
+      <c r="M7">
+        <v>30.98949954223633</v>
+      </c>
+      <c r="N7">
+        <v>12.16772727272727</v>
+      </c>
+      <c r="O7">
+        <v>43.15722681496361</v>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Axa, Paris</t>
+          <t>Sun Life Financial Inc</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>AXAHY</t>
-        </is>
-      </c>
-      <c r="C8">
-        <v>1.6056</v>
+          <t>SLF</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>financials</t>
+        </is>
       </c>
       <c r="D8">
-        <v>16.056</v>
+        <v>1.554090909090909</v>
       </c>
       <c r="E8">
-        <v>25.20000076293945</v>
+        <v>17.095</v>
       </c>
       <c r="F8">
-        <v>48.45999908447266</v>
+        <v>38.40999984741211</v>
       </c>
       <c r="G8">
-        <v>23.2599983215332</v>
+        <v>70.73999786376953</v>
+      </c>
+      <c r="H8">
+        <v>32.32999801635742</v>
+      </c>
+      <c r="I8">
+        <v>49.42499801635742</v>
+      </c>
+      <c r="J8">
+        <v>4.942499801635742</v>
+      </c>
+      <c r="K8">
+        <v>8</v>
+      </c>
+      <c r="L8">
+        <v>565.9199829101563</v>
+      </c>
+      <c r="M8">
+        <v>24.71249900817871</v>
+      </c>
+      <c r="N8">
+        <v>7.770454545454545</v>
+      </c>
+      <c r="O8">
+        <v>32.48295355363325</v>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Banco Bilbao Vizcaya Argentaria SA</t>
+          <t>Main Street Capital Corp</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>BBVA</t>
-        </is>
-      </c>
-      <c r="C9">
-        <v>0.4082727272727272</v>
+          <t>MAIN</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>financials</t>
+        </is>
       </c>
       <c r="D9">
-        <v>4.491</v>
+        <v>2.883181818181818</v>
       </c>
       <c r="E9">
-        <v>6.769999980926514</v>
+        <v>31.715</v>
       </c>
       <c r="F9">
-        <v>22.29000091552734</v>
+        <v>36.77000045776367</v>
       </c>
       <c r="G9">
-        <v>15.52000093460083</v>
+        <v>54.02000045776367</v>
+      </c>
+      <c r="H9">
+        <v>17.25</v>
+      </c>
+      <c r="I9">
+        <v>48.965</v>
+      </c>
+      <c r="J9">
+        <v>4.896500000000001</v>
+      </c>
+      <c r="K9">
+        <v>10</v>
+      </c>
+      <c r="L9">
+        <v>540.2000045776367</v>
+      </c>
+      <c r="M9">
+        <v>24.4825</v>
+      </c>
+      <c r="N9">
+        <v>14.41590909090909</v>
+      </c>
+      <c r="O9">
+        <v>38.89840909090909</v>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Banco De Chile</t>
+          <t>Woori Financial Group Inc</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>BCH</t>
-        </is>
-      </c>
-      <c r="C10">
-        <v>1.3828666</v>
+          <t>WF</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>financials</t>
+        </is>
       </c>
       <c r="D10">
-        <v>13.828666</v>
+        <v>2.34775</v>
       </c>
       <c r="E10">
-        <v>23.48333358764648</v>
+        <v>9.391</v>
       </c>
       <c r="F10">
-        <v>38.47000122070313</v>
+        <v>32</v>
       </c>
       <c r="G10">
-        <v>14.98666763305664</v>
+        <v>70.63999938964844</v>
+      </c>
+      <c r="H10">
+        <v>38.63999938964844</v>
+      </c>
+      <c r="I10">
+        <v>48.03099938964844</v>
+      </c>
+      <c r="J10">
+        <v>4.803099938964843</v>
+      </c>
+      <c r="K10">
+        <v>8</v>
+      </c>
+      <c r="L10">
+        <v>565.1199951171875</v>
+      </c>
+      <c r="M10">
+        <v>24.01549969482421</v>
+      </c>
+      <c r="N10">
+        <v>11.73875</v>
+      </c>
+      <c r="O10">
+        <v>35.75424969482421</v>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Franklin Resources Inc</t>
+          <t>United Overseas Bank Ltd</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>BEN</t>
-        </is>
-      </c>
-      <c r="C11">
-        <v>1.26</v>
+          <t>UOVEY</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>financials</t>
+        </is>
       </c>
       <c r="D11">
-        <v>13.86</v>
+        <v>1.8141</v>
       </c>
       <c r="E11">
-        <v>39.58000183105469</v>
+        <v>18.141</v>
       </c>
       <c r="F11">
-        <v>27.48999977111816</v>
+        <v>28.13999938964844</v>
       </c>
       <c r="G11">
-        <v>-12.09000205993652</v>
+        <v>57.65000152587891</v>
+      </c>
+      <c r="H11">
+        <v>29.51000213623047</v>
+      </c>
+      <c r="I11">
+        <v>47.65100213623047</v>
+      </c>
+      <c r="J11">
+        <v>4.765100213623047</v>
+      </c>
+      <c r="K11">
+        <v>9</v>
+      </c>
+      <c r="L11">
+        <v>518.8500137329102</v>
+      </c>
+      <c r="M11">
+        <v>23.82550106811523</v>
+      </c>
+      <c r="N11">
+        <v>9.070499999999999</v>
+      </c>
+      <c r="O11">
+        <v>32.89600106811523</v>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>BNP Paribas</t>
+          <t>The Bank of Nova Scotia</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>BNPQY</t>
-        </is>
-      </c>
-      <c r="C12">
-        <v>1.915888888888889</v>
+          <t>BNS</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>financials</t>
+        </is>
       </c>
       <c r="D12">
-        <v>17.243</v>
+        <v>2.5806</v>
       </c>
       <c r="E12">
-        <v>31.85000038146973</v>
+        <v>25.806</v>
       </c>
       <c r="F12">
-        <v>53.02999877929688</v>
+        <v>55.68000030517578</v>
       </c>
       <c r="G12">
-        <v>21.17999839782715</v>
+        <v>74.95999908447266</v>
+      </c>
+      <c r="H12">
+        <v>19.27999877929688</v>
+      </c>
+      <c r="I12">
+        <v>45.08599877929687</v>
+      </c>
+      <c r="J12">
+        <v>4.508599877929687</v>
+      </c>
+      <c r="K12">
+        <v>7</v>
+      </c>
+      <c r="L12">
+        <v>524.7199935913086</v>
+      </c>
+      <c r="M12">
+        <v>22.54299938964844</v>
+      </c>
+      <c r="N12">
+        <v>12.903</v>
+      </c>
+      <c r="O12">
+        <v>35.44599938964843</v>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>The Bank of Nova Scotia</t>
+          <t>Fidelity National Financial Inc</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>BNS</t>
-        </is>
-      </c>
-      <c r="C13">
-        <v>2.5806</v>
+          <t>FNF</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>financials</t>
+        </is>
       </c>
       <c r="D13">
-        <v>25.806</v>
+        <v>1.269100090909091</v>
       </c>
       <c r="E13">
-        <v>55.68000030517578</v>
+        <v>13.960101</v>
       </c>
       <c r="F13">
-        <v>75.13999938964844</v>
+        <v>22.73556709289551</v>
       </c>
       <c r="G13">
-        <v>19.45999908447266</v>
+        <v>51.54000091552734</v>
+      </c>
+      <c r="H13">
+        <v>28.80443382263184</v>
+      </c>
+      <c r="I13">
+        <v>42.76453482263184</v>
+      </c>
+      <c r="J13">
+        <v>4.276453482263184</v>
+      </c>
+      <c r="K13">
+        <v>10</v>
+      </c>
+      <c r="L13">
+        <v>515.4000091552734</v>
+      </c>
+      <c r="M13">
+        <v>21.38226741131592</v>
+      </c>
+      <c r="N13">
+        <v>6.345500454545454</v>
+      </c>
+      <c r="O13">
+        <v>27.72776786586138</v>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Banco Santander-Chile</t>
+          <t>Allianz SE</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>BSAC</t>
-        </is>
-      </c>
-      <c r="C14">
-        <v>1.117222222222222</v>
+          <t>ALIZY</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>financials</t>
+        </is>
       </c>
       <c r="D14">
-        <v>10.055</v>
+        <v>1.1421</v>
       </c>
       <c r="E14">
-        <v>21.8700008392334</v>
+        <v>11.421</v>
       </c>
       <c r="F14">
-        <v>33.59999847412109</v>
+        <v>16.47999954223633</v>
       </c>
       <c r="G14">
-        <v>11.7299976348877</v>
+        <v>45.29000091552734</v>
+      </c>
+      <c r="H14">
+        <v>28.81000137329102</v>
+      </c>
+      <c r="I14">
+        <v>40.23100137329101</v>
+      </c>
+      <c r="J14">
+        <v>4.023100137329101</v>
+      </c>
+      <c r="K14">
+        <v>12</v>
+      </c>
+      <c r="L14">
+        <v>543.4800109863281</v>
+      </c>
+      <c r="M14">
+        <v>20.11550068664551</v>
+      </c>
+      <c r="N14">
+        <v>5.710500000000001</v>
+      </c>
+      <c r="O14">
+        <v>25.82600068664551</v>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Blackstone Secured Lending Fund</t>
+          <t>CNA Financial Corp</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>BXSL</t>
-        </is>
-      </c>
-      <c r="C15">
-        <v>2.218333333333333</v>
+          <t>CNA</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>financials</t>
+        </is>
       </c>
       <c r="D15">
-        <v>13.31</v>
+        <v>2.987272727272727</v>
+      </c>
+      <c r="E15">
+        <v>32.86</v>
       </c>
       <c r="F15">
-        <v>24.14999961853027</v>
+        <v>41.5</v>
+      </c>
+      <c r="G15">
+        <v>48.75</v>
+      </c>
+      <c r="H15">
+        <v>7.25</v>
+      </c>
+      <c r="I15">
+        <v>40.11</v>
+      </c>
+      <c r="J15">
+        <v>4.011</v>
+      </c>
+      <c r="K15">
+        <v>11</v>
+      </c>
+      <c r="L15">
+        <v>536.25</v>
+      </c>
+      <c r="M15">
+        <v>20.055</v>
+      </c>
+      <c r="N15">
+        <v>14.93636363636364</v>
+      </c>
+      <c r="O15">
+        <v>34.99136363636364</v>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Grupo Cibest S.A</t>
+          <t>Axa, Paris</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>CIB</t>
-        </is>
-      </c>
-      <c r="C16">
-        <v>2.433545454545455</v>
+          <t>AXAHY</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>financials</t>
+        </is>
       </c>
       <c r="D16">
-        <v>26.769</v>
+        <v>1.6056</v>
       </c>
       <c r="E16">
-        <v>36.68000030517578</v>
+        <v>16.056</v>
       </c>
       <c r="F16">
-        <v>73.56999969482422</v>
+        <v>25.20000076293945</v>
       </c>
       <c r="G16">
-        <v>36.88999938964844</v>
+        <v>47.54999923706055</v>
+      </c>
+      <c r="H16">
+        <v>22.34999847412109</v>
+      </c>
+      <c r="I16">
+        <v>38.40599847412109</v>
+      </c>
+      <c r="J16">
+        <v>3.840599847412109</v>
+      </c>
+      <c r="K16">
+        <v>11</v>
+      </c>
+      <c r="L16">
+        <v>523.049991607666</v>
+      </c>
+      <c r="M16">
+        <v>19.20299923706055</v>
+      </c>
+      <c r="N16">
+        <v>8.027999999999999</v>
+      </c>
+      <c r="O16">
+        <v>27.23099923706054</v>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>CNA Financial Corp</t>
+          <t>BNP Paribas</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>CNA</t>
-        </is>
-      </c>
-      <c r="C17">
-        <v>2.987272727272727</v>
+          <t>BNPQY</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>financials</t>
+        </is>
       </c>
       <c r="D17">
-        <v>32.86</v>
+        <v>1.915888888888889</v>
       </c>
       <c r="E17">
-        <v>41.5</v>
+        <v>17.243</v>
       </c>
       <c r="F17">
-        <v>48.06000137329102</v>
+        <v>31.85000038146973</v>
       </c>
       <c r="G17">
-        <v>6.560001373291016</v>
+        <v>51.86999893188477</v>
+      </c>
+      <c r="H17">
+        <v>20.01999855041504</v>
+      </c>
+      <c r="I17">
+        <v>37.26299855041504</v>
+      </c>
+      <c r="J17">
+        <v>3.726299855041504</v>
+      </c>
+      <c r="K17">
+        <v>10</v>
+      </c>
+      <c r="L17">
+        <v>518.6999893188477</v>
+      </c>
+      <c r="M17">
+        <v>18.63149927520752</v>
+      </c>
+      <c r="N17">
+        <v>9.579444444444444</v>
+      </c>
+      <c r="O17">
+        <v>28.21094371965197</v>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Columbia Banking System Inc</t>
+          <t>Intesa Sanpaolo SPA</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>COLB</t>
-        </is>
-      </c>
-      <c r="C18">
-        <v>1.171818181818182</v>
+          <t>ISNPY</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>financials</t>
+        </is>
       </c>
       <c r="D18">
-        <v>12.89</v>
+        <v>1.340444444444444</v>
       </c>
       <c r="E18">
-        <v>44.68000030517578</v>
+        <v>12.064</v>
       </c>
       <c r="F18">
-        <v>29</v>
+        <v>15.22999954223633</v>
       </c>
       <c r="G18">
-        <v>-15.68000030517578</v>
+        <v>39.29000091552734</v>
+      </c>
+      <c r="H18">
+        <v>24.06000137329102</v>
+      </c>
+      <c r="I18">
+        <v>36.12400137329102</v>
+      </c>
+      <c r="J18">
+        <v>3.612400137329101</v>
+      </c>
+      <c r="K18">
+        <v>13</v>
+      </c>
+      <c r="L18">
+        <v>510.7700119018555</v>
+      </c>
+      <c r="M18">
+        <v>18.06200068664551</v>
+      </c>
+      <c r="N18">
+        <v>6.702222222222222</v>
+      </c>
+      <c r="O18">
+        <v>24.76422290886773</v>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>DBS Group Holdings Ltd</t>
+          <t>Prudential Financial Inc</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>DBSDY</t>
-        </is>
-      </c>
-      <c r="C19">
-        <v>3.441421636363637</v>
+          <t>PRU</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>financials</t>
+        </is>
       </c>
       <c r="D19">
-        <v>37.855638</v>
+        <v>3.954545454545455</v>
       </c>
       <c r="E19">
-        <v>43.40909194946289</v>
+        <v>43.5</v>
       </c>
       <c r="F19">
-        <v>178.3999938964844</v>
+        <v>104.0599975585938</v>
       </c>
       <c r="G19">
-        <v>134.9909019470215</v>
+        <v>94.34999847412109</v>
+      </c>
+      <c r="H19">
+        <v>-9.709999084472656</v>
+      </c>
+      <c r="I19">
+        <v>33.79000091552734</v>
+      </c>
+      <c r="J19">
+        <v>3.379000091552734</v>
+      </c>
+      <c r="K19">
+        <v>6</v>
+      </c>
+      <c r="L19">
+        <v>566.0999908447266</v>
+      </c>
+      <c r="M19">
+        <v>16.89500045776367</v>
+      </c>
+      <c r="N19">
+        <v>19.77272727272727</v>
+      </c>
+      <c r="O19">
+        <v>36.66772773049095</v>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Danske Bank AS</t>
+          <t>Jefferies Financial Group Inc</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>DNKEY</t>
-        </is>
-      </c>
-      <c r="C20">
-        <v>0.7968000000000001</v>
+          <t>JEF</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>financials</t>
+        </is>
       </c>
       <c r="D20">
-        <v>7.968</v>
+        <v>0.7636609090909091</v>
       </c>
       <c r="E20">
-        <v>15.18000030517578</v>
+        <v>8.400269999999999</v>
       </c>
       <c r="F20">
-        <v>25.70000076293945</v>
+        <v>20.81229782104492</v>
       </c>
       <c r="G20">
-        <v>10.52000045776367</v>
+        <v>45.68999862670898</v>
+      </c>
+      <c r="H20">
+        <v>24.87770080566406</v>
+      </c>
+      <c r="I20">
+        <v>33.27797080566406</v>
+      </c>
+      <c r="J20">
+        <v>3.327797080566406</v>
+      </c>
+      <c r="K20">
+        <v>11</v>
+      </c>
+      <c r="L20">
+        <v>502.5899848937988</v>
+      </c>
+      <c r="M20">
+        <v>16.63898540283203</v>
+      </c>
+      <c r="N20">
+        <v>3.818304545454545</v>
+      </c>
+      <c r="O20">
+        <v>20.45728994828658</v>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Fidelity National Financial Inc</t>
+          <t>Schweizerische Rueckversicherungs-Gesellschaft, Zu</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>FNF</t>
-        </is>
-      </c>
-      <c r="C21">
-        <v>1.269100090909091</v>
+          <t>SSREY</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>financials</t>
+        </is>
       </c>
       <c r="D21">
-        <v>13.960101</v>
+        <v>1.5439</v>
       </c>
       <c r="E21">
-        <v>22.73556709289551</v>
+        <v>15.439</v>
       </c>
       <c r="F21">
-        <v>50.63000106811523</v>
+        <v>23.76000022888184</v>
       </c>
       <c r="G21">
-        <v>27.89443397521973</v>
+        <v>40.95999908447266</v>
+      </c>
+      <c r="H21">
+        <v>17.19999885559082</v>
+      </c>
+      <c r="I21">
+        <v>32.63899885559082</v>
+      </c>
+      <c r="J21">
+        <v>3.263899885559082</v>
+      </c>
+      <c r="K21">
+        <v>13</v>
+      </c>
+      <c r="L21">
+        <v>532.4799880981445</v>
+      </c>
+      <c r="M21">
+        <v>16.31949942779541</v>
+      </c>
+      <c r="N21">
+        <v>7.7195</v>
+      </c>
+      <c r="O21">
+        <v>24.03899942779541</v>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Huntington Bancshares Inc</t>
+          <t>Manulife Financial Corp</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>HBAN</t>
-        </is>
-      </c>
-      <c r="C22">
-        <v>0.4990909090909091</v>
+          <t>MFC</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>financials</t>
+        </is>
       </c>
       <c r="D22">
-        <v>5.49</v>
+        <v>0.7749090909090909</v>
       </c>
       <c r="E22">
-        <v>13.22000026702881</v>
+        <v>8.523999999999999</v>
       </c>
       <c r="F22">
-        <v>16.81999969482422</v>
+        <v>17.81999969482422</v>
       </c>
       <c r="G22">
-        <v>3.59999942779541</v>
+        <v>38.65000152587891</v>
+      </c>
+      <c r="H22">
+        <v>20.83000183105469</v>
+      </c>
+      <c r="I22">
+        <v>29.35400183105469</v>
+      </c>
+      <c r="J22">
+        <v>2.935400183105469</v>
+      </c>
+      <c r="K22">
+        <v>13</v>
+      </c>
+      <c r="L22">
+        <v>502.4500198364258</v>
+      </c>
+      <c r="M22">
+        <v>14.67700091552734</v>
+      </c>
+      <c r="N22">
+        <v>3.874545454545455</v>
+      </c>
+      <c r="O22">
+        <v>18.5515463700728</v>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>HSBC Holdings PLC</t>
+          <t>Banco De Chile</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>HSBC</t>
-        </is>
-      </c>
-      <c r="C23">
-        <v>2.268181818181818</v>
+          <t>BCH</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>financials</t>
+        </is>
       </c>
       <c r="D23">
-        <v>24.95</v>
+        <v>1.3828666</v>
       </c>
       <c r="E23">
-        <v>40.18000030517578</v>
+        <v>13.828666</v>
       </c>
       <c r="F23">
-        <v>90.47000122070313</v>
+        <v>23.48333358764648</v>
       </c>
       <c r="G23">
-        <v>50.29000091552734</v>
+        <v>37.7599983215332</v>
+      </c>
+      <c r="H23">
+        <v>14.27666473388672</v>
+      </c>
+      <c r="I23">
+        <v>28.10533073388672</v>
+      </c>
+      <c r="J23">
+        <v>2.810533073388672</v>
+      </c>
+      <c r="K23">
+        <v>14</v>
+      </c>
+      <c r="L23">
+        <v>528.6399765014648</v>
+      </c>
+      <c r="M23">
+        <v>14.05266536694336</v>
+      </c>
+      <c r="N23">
+        <v>6.914333</v>
+      </c>
+      <c r="O23">
+        <v>20.96699836694336</v>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>ING Groep NV</t>
+          <t>Lazard Inc</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>ING</t>
-        </is>
-      </c>
-      <c r="C24">
-        <v>0.8558</v>
+          <t>LAZ</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>financials</t>
+        </is>
       </c>
       <c r="D24">
-        <v>8.558</v>
+        <v>1.957272727272727</v>
       </c>
       <c r="E24">
-        <v>14.10000038146973</v>
+        <v>21.53</v>
       </c>
       <c r="F24">
-        <v>28.07999992370605</v>
+        <v>41.09000015258789</v>
       </c>
       <c r="G24">
-        <v>13.97999954223633</v>
+        <v>47.04000091552734</v>
+      </c>
+      <c r="H24">
+        <v>5.950000762939453</v>
+      </c>
+      <c r="I24">
+        <v>27.48000076293945</v>
+      </c>
+      <c r="J24">
+        <v>2.748000076293946</v>
+      </c>
+      <c r="K24">
+        <v>11</v>
+      </c>
+      <c r="L24">
+        <v>517.4400100708008</v>
+      </c>
+      <c r="M24">
+        <v>13.74000038146973</v>
+      </c>
+      <c r="N24">
+        <v>9.786363636363637</v>
+      </c>
+      <c r="O24">
+        <v>23.52636401783337</v>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Intesa Sanpaolo SPA</t>
+          <t>Swedbank AB</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>ISNPY</t>
-        </is>
-      </c>
-      <c r="C25">
-        <v>1.340444444444444</v>
+          <t>SWDBY</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>financials</t>
+        </is>
       </c>
       <c r="D25">
-        <v>12.064</v>
+        <v>1.6139</v>
       </c>
       <c r="E25">
-        <v>15.22999954223633</v>
+        <v>16.139</v>
       </c>
       <c r="F25">
-        <v>40.31999969482422</v>
+        <v>24.14999961853027</v>
       </c>
       <c r="G25">
-        <v>25.09000015258789</v>
+        <v>34.81000137329102</v>
+      </c>
+      <c r="H25">
+        <v>10.66000175476074</v>
+      </c>
+      <c r="I25">
+        <v>26.79900175476074</v>
+      </c>
+      <c r="J25">
+        <v>2.679900175476074</v>
+      </c>
+      <c r="K25">
+        <v>15</v>
+      </c>
+      <c r="L25">
+        <v>522.1500205993652</v>
+      </c>
+      <c r="M25">
+        <v>13.39950087738037</v>
+      </c>
+      <c r="N25">
+        <v>8.069500000000001</v>
+      </c>
+      <c r="O25">
+        <v>21.46900087738037</v>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Jefferies Financial Group Inc</t>
+          <t>Truist Financial Corp</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>JEF</t>
-        </is>
-      </c>
-      <c r="C26">
-        <v>0.7636609090909091</v>
+          <t>TFC</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>financials</t>
+        </is>
       </c>
       <c r="D26">
-        <v>8.400269999999999</v>
+        <v>1.620909090909091</v>
       </c>
       <c r="E26">
-        <v>20.81229782104492</v>
+        <v>17.83</v>
       </c>
       <c r="F26">
-        <v>47.0099983215332</v>
+        <v>47.02000045776367</v>
       </c>
       <c r="G26">
-        <v>26.19770050048828</v>
+        <v>51.40000152587891</v>
+      </c>
+      <c r="H26">
+        <v>4.380001068115234</v>
+      </c>
+      <c r="I26">
+        <v>22.21000106811524</v>
+      </c>
+      <c r="J26">
+        <v>2.221000106811524</v>
+      </c>
+      <c r="K26">
+        <v>10</v>
+      </c>
+      <c r="L26">
+        <v>514.0000152587891</v>
+      </c>
+      <c r="M26">
+        <v>11.10500053405762</v>
+      </c>
+      <c r="N26">
+        <v>8.104545454545454</v>
+      </c>
+      <c r="O26">
+        <v>19.20954598860307</v>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>KeyCorp</t>
+          <t>ING Groep NV</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>KEY</t>
-        </is>
-      </c>
-      <c r="C27">
-        <v>0.6231818181818182</v>
+          <t>ING</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>financials</t>
+        </is>
       </c>
       <c r="D27">
-        <v>6.855</v>
+        <v>0.8558</v>
       </c>
       <c r="E27">
-        <v>18.27000045776367</v>
+        <v>8.558</v>
       </c>
       <c r="F27">
-        <v>22.04000091552734</v>
+        <v>14.10000038146973</v>
       </c>
       <c r="G27">
-        <v>3.770000457763672</v>
+        <v>27.71999931335449</v>
+      </c>
+      <c r="H27">
+        <v>13.61999893188477</v>
+      </c>
+      <c r="I27">
+        <v>22.17799893188477</v>
+      </c>
+      <c r="J27">
+        <v>2.217799893188476</v>
+      </c>
+      <c r="K27">
+        <v>19</v>
+      </c>
+      <c r="L27">
+        <v>526.6799869537354</v>
+      </c>
+      <c r="M27">
+        <v>11.08899946594238</v>
+      </c>
+      <c r="N27">
+        <v>4.279</v>
+      </c>
+      <c r="O27">
+        <v>15.36799946594238</v>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Lazard Inc</t>
+          <t>U.S. Bancorp</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>LAZ</t>
-        </is>
-      </c>
-      <c r="C28">
-        <v>1.957272727272727</v>
+          <t>USB</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>financials</t>
+        </is>
       </c>
       <c r="D28">
-        <v>21.53</v>
+        <v>1.516818181818182</v>
       </c>
       <c r="E28">
-        <v>41.09000015258789</v>
+        <v>16.685</v>
       </c>
       <c r="F28">
-        <v>47.40999984741211</v>
+        <v>51.36999893188477</v>
       </c>
       <c r="G28">
-        <v>6.319999694824219</v>
+        <v>56.63000106811523</v>
+      </c>
+      <c r="H28">
+        <v>5.260002136230469</v>
+      </c>
+      <c r="I28">
+        <v>21.94500213623047</v>
+      </c>
+      <c r="J28">
+        <v>2.194500213623047</v>
+      </c>
+      <c r="K28">
+        <v>9</v>
+      </c>
+      <c r="L28">
+        <v>509.6700096130371</v>
+      </c>
+      <c r="M28">
+        <v>10.97250106811524</v>
+      </c>
+      <c r="N28">
+        <v>7.584090909090909</v>
+      </c>
+      <c r="O28">
+        <v>18.55659197720615</v>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Lincoln National Corp</t>
+          <t>Banco Santander-Chile</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>LNC</t>
-        </is>
-      </c>
-      <c r="C29">
-        <v>1.44</v>
+          <t>BSAC</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>financials</t>
+        </is>
       </c>
       <c r="D29">
-        <v>15.84</v>
+        <v>1.117222222222222</v>
       </c>
       <c r="E29">
-        <v>66.26999664306641</v>
+        <v>10.055</v>
       </c>
       <c r="F29">
-        <v>36.83000183105469</v>
+        <v>21.8700008392334</v>
       </c>
       <c r="G29">
-        <v>-29.43999481201172</v>
+        <v>33.43999862670898</v>
+      </c>
+      <c r="H29">
+        <v>11.56999778747559</v>
+      </c>
+      <c r="I29">
+        <v>21.62499778747559</v>
+      </c>
+      <c r="J29">
+        <v>2.162499778747558</v>
+      </c>
+      <c r="K29">
+        <v>15</v>
+      </c>
+      <c r="L29">
+        <v>501.5999794006348</v>
+      </c>
+      <c r="M29">
+        <v>10.81249889373779</v>
+      </c>
+      <c r="N29">
+        <v>5.58611111111111</v>
+      </c>
+      <c r="O29">
+        <v>16.3986100048489</v>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Main Street Capital Corp</t>
+          <t>Regions Financial Corp</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>MAIN</t>
-        </is>
-      </c>
-      <c r="C30">
-        <v>2.883181818181818</v>
+          <t>RF</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>financials</t>
+        </is>
       </c>
       <c r="D30">
-        <v>31.715</v>
+        <v>0.6113636363636363</v>
       </c>
       <c r="E30">
-        <v>36.77000045776367</v>
+        <v>6.725000000000001</v>
       </c>
       <c r="F30">
-        <v>54.65000152587891</v>
+        <v>14.35999965667725</v>
       </c>
       <c r="G30">
-        <v>17.88000106811523</v>
+        <v>28.39999961853027</v>
+      </c>
+      <c r="H30">
+        <v>14.03999996185303</v>
+      </c>
+      <c r="I30">
+        <v>20.76499996185303</v>
+      </c>
+      <c r="J30">
+        <v>2.076499996185303</v>
+      </c>
+      <c r="K30">
+        <v>18</v>
+      </c>
+      <c r="L30">
+        <v>511.1999931335449</v>
+      </c>
+      <c r="M30">
+        <v>10.38249998092651</v>
+      </c>
+      <c r="N30">
+        <v>3.056818181818182</v>
+      </c>
+      <c r="O30">
+        <v>13.4393181627447</v>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Moelis &amp; Co</t>
+          <t>Banco Bilbao Vizcaya Argentaria SA</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>MC</t>
-        </is>
-      </c>
-      <c r="C31">
-        <v>3.109363636363637</v>
+          <t>BBVA</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>financials</t>
+        </is>
       </c>
       <c r="D31">
-        <v>34.203</v>
+        <v>0.4082727272727272</v>
       </c>
       <c r="E31">
-        <v>33.90000152587891</v>
+        <v>4.491</v>
       </c>
       <c r="F31">
-        <v>67.16999816894531</v>
+        <v>6.769999980926514</v>
       </c>
       <c r="G31">
-        <v>33.26999664306641</v>
+        <v>21.6200008392334</v>
+      </c>
+      <c r="H31">
+        <v>14.85000085830688</v>
+      </c>
+      <c r="I31">
+        <v>19.34100085830688</v>
+      </c>
+      <c r="J31">
+        <v>1.934100085830688</v>
+      </c>
+      <c r="K31">
+        <v>24</v>
+      </c>
+      <c r="L31">
+        <v>518.8800201416016</v>
+      </c>
+      <c r="M31">
+        <v>9.670500429153442</v>
+      </c>
+      <c r="N31">
+        <v>2.041363636363636</v>
+      </c>
+      <c r="O31">
+        <v>11.71186406551708</v>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Manulife Financial Corp</t>
+          <t>ARES CAPITAL CORPORATION</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>MFC</t>
-        </is>
-      </c>
-      <c r="C32">
-        <v>0.7749090909090909</v>
+          <t>ARCC</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>financials</t>
+        </is>
       </c>
       <c r="D32">
-        <v>8.523999999999999</v>
+        <v>1.564545454545454</v>
       </c>
       <c r="E32">
-        <v>17.81999969482422</v>
+        <v>17.21</v>
       </c>
       <c r="F32">
-        <v>38.31000137329102</v>
+        <v>16.48999977111816</v>
       </c>
       <c r="G32">
-        <v>20.4900016784668</v>
+        <v>18.6200008392334</v>
+      </c>
+      <c r="H32">
+        <v>2.130001068115234</v>
+      </c>
+      <c r="I32">
+        <v>19.34000106811524</v>
+      </c>
+      <c r="J32">
+        <v>1.934000106811524</v>
+      </c>
+      <c r="K32">
+        <v>27</v>
+      </c>
+      <c r="L32">
+        <v>502.7400226593018</v>
+      </c>
+      <c r="M32">
+        <v>9.670000534057618</v>
+      </c>
+      <c r="N32">
+        <v>7.822727272727272</v>
+      </c>
+      <c r="O32">
+        <v>17.49272780678489</v>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
       </c>
     </row>
     <row r="33">
@@ -1233,398 +2245,845 @@
           <t>NLY</t>
         </is>
       </c>
-      <c r="C33">
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>financials</t>
+        </is>
+      </c>
+      <c r="D33">
         <v>3.343636363636364</v>
       </c>
-      <c r="D33">
+      <c r="E33">
         <v>36.78</v>
       </c>
-      <c r="E33">
+      <c r="F33">
         <v>39.88000106811523</v>
       </c>
-      <c r="F33">
-        <v>22.6299991607666</v>
-      </c>
       <c r="G33">
-        <v>-17.25000190734863</v>
+        <v>22.43000030517578</v>
+      </c>
+      <c r="H33">
+        <v>-17.45000076293945</v>
+      </c>
+      <c r="I33">
+        <v>19.32999923706055</v>
+      </c>
+      <c r="J33">
+        <v>1.932999923706055</v>
+      </c>
+      <c r="K33">
+        <v>23</v>
+      </c>
+      <c r="L33">
+        <v>515.890007019043</v>
+      </c>
+      <c r="M33">
+        <v>9.664999618530274</v>
+      </c>
+      <c r="N33">
+        <v>16.71818181818182</v>
+      </c>
+      <c r="O33">
+        <v>26.38318143671209</v>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>NatWest Group plc</t>
+          <t>Danske Bank AS</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>NWG</t>
-        </is>
-      </c>
-      <c r="C34">
-        <v>0.4551158888888889</v>
+          <t>DNKEY</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>financials</t>
+        </is>
       </c>
       <c r="D34">
-        <v>4.096043</v>
+        <v>0.7968000000000001</v>
       </c>
       <c r="E34">
-        <v>5.959052085876465</v>
+        <v>7.968</v>
       </c>
       <c r="F34">
-        <v>15.97000026702881</v>
+        <v>15.18000030517578</v>
       </c>
       <c r="G34">
-        <v>10.01094818115234</v>
+        <v>25.1200008392334</v>
+      </c>
+      <c r="H34">
+        <v>9.940000534057617</v>
+      </c>
+      <c r="I34">
+        <v>17.90800053405762</v>
+      </c>
+      <c r="J34">
+        <v>1.790800053405762</v>
+      </c>
+      <c r="K34">
+        <v>20</v>
+      </c>
+      <c r="L34">
+        <v>502.400016784668</v>
+      </c>
+      <c r="M34">
+        <v>8.954000267028809</v>
+      </c>
+      <c r="N34">
+        <v>3.984</v>
+      </c>
+      <c r="O34">
+        <v>12.93800026702881</v>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>OneMain Holdings Inc</t>
+          <t>Absa Group Ltd</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>OMF</t>
-        </is>
-      </c>
-      <c r="C35">
-        <v>4.45375</v>
+          <t>AGRPY</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>financials</t>
+        </is>
       </c>
       <c r="D35">
-        <v>35.63</v>
+        <v>1.1849</v>
       </c>
       <c r="E35">
-        <v>22.13999938964844</v>
+        <v>11.849</v>
       </c>
       <c r="F35">
-        <v>59.70999908447266</v>
+        <v>25</v>
       </c>
       <c r="G35">
-        <v>37.56999969482422</v>
+        <v>28.64999961853027</v>
+      </c>
+      <c r="H35">
+        <v>3.649999618530273</v>
+      </c>
+      <c r="I35">
+        <v>15.49899961853027</v>
+      </c>
+      <c r="J35">
+        <v>1.549899961853027</v>
+      </c>
+      <c r="K35">
+        <v>18</v>
+      </c>
+      <c r="L35">
+        <v>515.6999931335449</v>
+      </c>
+      <c r="M35">
+        <v>7.749499809265137</v>
+      </c>
+      <c r="N35">
+        <v>5.9245</v>
+      </c>
+      <c r="O35">
+        <v>13.67399980926514</v>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Bank OZK</t>
+          <t>Starwood Property Trust Inc</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>OZK</t>
-        </is>
-      </c>
-      <c r="C36">
-        <v>1.082818181818182</v>
+          <t>STWD</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>financials</t>
+        </is>
       </c>
       <c r="D36">
-        <v>11.911</v>
+        <v>1.745454545454545</v>
       </c>
       <c r="E36">
-        <v>52.59000015258789</v>
+        <v>19.2</v>
       </c>
       <c r="F36">
-        <v>47.52000045776367</v>
+        <v>21.95000076293945</v>
       </c>
       <c r="G36">
-        <v>-5.069999694824219</v>
+        <v>18.13999938964844</v>
+      </c>
+      <c r="H36">
+        <v>-3.810001373291016</v>
+      </c>
+      <c r="I36">
+        <v>15.38999862670898</v>
+      </c>
+      <c r="J36">
+        <v>1.538999862670898</v>
+      </c>
+      <c r="K36">
+        <v>28</v>
+      </c>
+      <c r="L36">
+        <v>507.9199829101563</v>
+      </c>
+      <c r="M36">
+        <v>7.694999313354492</v>
+      </c>
+      <c r="N36">
+        <v>8.727272727272727</v>
+      </c>
+      <c r="O36">
+        <v>16.42227204062722</v>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Prudential Financial Inc</t>
+          <t>ANZ Group Holdings Limited</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>PRU</t>
-        </is>
-      </c>
-      <c r="C37">
-        <v>3.954545454545455</v>
+          <t>ANZGY</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>financials</t>
+        </is>
       </c>
       <c r="D37">
-        <v>43.5</v>
+        <v>0.9964000000000001</v>
       </c>
       <c r="E37">
-        <v>104.0599975585938</v>
+        <v>9.964</v>
       </c>
       <c r="F37">
-        <v>94.84999847412109</v>
+        <v>21.84000015258789</v>
       </c>
       <c r="G37">
-        <v>-9.209999084472656</v>
+        <v>25.86000061035156</v>
+      </c>
+      <c r="H37">
+        <v>4.020000457763672</v>
+      </c>
+      <c r="I37">
+        <v>13.98400045776367</v>
+      </c>
+      <c r="J37">
+        <v>1.398400045776367</v>
+      </c>
+      <c r="K37">
+        <v>20</v>
+      </c>
+      <c r="L37">
+        <v>517.2000122070313</v>
+      </c>
+      <c r="M37">
+        <v>6.992000228881836</v>
+      </c>
+      <c r="N37">
+        <v>4.982</v>
+      </c>
+      <c r="O37">
+        <v>11.97400022888184</v>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Regions Financial Corp</t>
+          <t>NatWest Group plc</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>RF</t>
-        </is>
-      </c>
-      <c r="C38">
-        <v>0.6113636363636363</v>
+          <t>NWG</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>financials</t>
+        </is>
       </c>
       <c r="D38">
-        <v>6.725000000000001</v>
+        <v>0.4551158888888889</v>
       </c>
       <c r="E38">
-        <v>14.35999965667725</v>
+        <v>4.096043</v>
       </c>
       <c r="F38">
-        <v>28.20999908447266</v>
+        <v>5.959052085876465</v>
       </c>
       <c r="G38">
-        <v>13.84999942779541</v>
+        <v>15.68000030517578</v>
+      </c>
+      <c r="H38">
+        <v>9.720948219299316</v>
+      </c>
+      <c r="I38">
+        <v>13.81699121929932</v>
+      </c>
+      <c r="J38">
+        <v>1.381699121929932</v>
+      </c>
+      <c r="K38">
+        <v>32</v>
+      </c>
+      <c r="L38">
+        <v>501.760009765625</v>
+      </c>
+      <c r="M38">
+        <v>6.908495609649659</v>
+      </c>
+      <c r="N38">
+        <v>2.275579444444444</v>
+      </c>
+      <c r="O38">
+        <v>9.184075054094103</v>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Sun Life Financial Inc</t>
+          <t>Atlantic Union Bankshares Corp</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>SLF</t>
-        </is>
-      </c>
-      <c r="C39">
-        <v>1.554090909090909</v>
+          <t>AUB</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>financials</t>
+        </is>
       </c>
       <c r="D39">
-        <v>17.095</v>
+        <v>0.9781818181818183</v>
       </c>
       <c r="E39">
-        <v>38.40999984741211</v>
+        <v>10.76</v>
       </c>
       <c r="F39">
-        <v>70.48000335693359</v>
+        <v>35.7400016784668</v>
       </c>
       <c r="G39">
-        <v>32.07000350952148</v>
+        <v>37.90999984741211</v>
+      </c>
+      <c r="H39">
+        <v>2.169998168945313</v>
+      </c>
+      <c r="I39">
+        <v>12.92999816894531</v>
+      </c>
+      <c r="J39">
+        <v>1.292999816894531</v>
+      </c>
+      <c r="K39">
+        <v>14</v>
+      </c>
+      <c r="L39">
+        <v>530.7399978637695</v>
+      </c>
+      <c r="M39">
+        <v>6.464999084472655</v>
+      </c>
+      <c r="N39">
+        <v>4.890909090909092</v>
+      </c>
+      <c r="O39">
+        <v>11.35590817538175</v>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Schweizerische Rueckversicherungs-Gesellschaft, Zu</t>
+          <t>Aviva PLC</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>SSREY</t>
-        </is>
-      </c>
-      <c r="C40">
-        <v>1.5439</v>
+          <t>AVVIY</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>financials</t>
+        </is>
       </c>
       <c r="D40">
-        <v>15.439</v>
+        <v>0.9795454545454545</v>
       </c>
       <c r="E40">
-        <v>23.76000022888184</v>
+        <v>10.775</v>
       </c>
       <c r="F40">
-        <v>41.7400016784668</v>
+        <v>15.53947353363037</v>
       </c>
       <c r="G40">
-        <v>17.98000144958496</v>
+        <v>17.02000045776367</v>
+      </c>
+      <c r="H40">
+        <v>1.480526924133301</v>
+      </c>
+      <c r="I40">
+        <v>12.2555269241333</v>
+      </c>
+      <c r="J40">
+        <v>1.22555269241333</v>
+      </c>
+      <c r="K40">
+        <v>30</v>
+      </c>
+      <c r="L40">
+        <v>510.6000137329102</v>
+      </c>
+      <c r="M40">
+        <v>6.127763462066651</v>
+      </c>
+      <c r="N40">
+        <v>4.897727272727272</v>
+      </c>
+      <c r="O40">
+        <v>11.02549073479392</v>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Starwood Property Trust Inc</t>
+          <t>KeyCorp</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>STWD</t>
-        </is>
-      </c>
-      <c r="C41">
-        <v>1.745454545454545</v>
+          <t>KEY</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>financials</t>
+        </is>
       </c>
       <c r="D41">
-        <v>19.2</v>
+        <v>0.6231818181818182</v>
       </c>
       <c r="E41">
-        <v>21.95000076293945</v>
+        <v>6.855</v>
       </c>
       <c r="F41">
-        <v>18.23999977111816</v>
+        <v>18.27000045776367</v>
       </c>
       <c r="G41">
-        <v>-3.710000991821289</v>
+        <v>22.01000022888184</v>
+      </c>
+      <c r="H41">
+        <v>3.739999771118164</v>
+      </c>
+      <c r="I41">
+        <v>10.59499977111816</v>
+      </c>
+      <c r="J41">
+        <v>1.059499977111817</v>
+      </c>
+      <c r="K41">
+        <v>23</v>
+      </c>
+      <c r="L41">
+        <v>506.2300052642822</v>
+      </c>
+      <c r="M41">
+        <v>5.297499885559082</v>
+      </c>
+      <c r="N41">
+        <v>3.115909090909091</v>
+      </c>
+      <c r="O41">
+        <v>8.413408976468173</v>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Swedbank AB</t>
+          <t>Huntington Bancshares Inc</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>SWDBY</t>
-        </is>
-      </c>
-      <c r="C42">
-        <v>1.6139</v>
+          <t>HBAN</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>financials</t>
+        </is>
       </c>
       <c r="D42">
-        <v>16.139</v>
+        <v>0.4990909090909091</v>
       </c>
       <c r="E42">
-        <v>24.14999961853027</v>
+        <v>5.49</v>
       </c>
       <c r="F42">
-        <v>35.63999938964844</v>
+        <v>13.22000026702881</v>
       </c>
       <c r="G42">
-        <v>11.48999977111816</v>
+        <v>16.82999992370605</v>
+      </c>
+      <c r="H42">
+        <v>3.609999656677246</v>
+      </c>
+      <c r="I42">
+        <v>9.099999656677246</v>
+      </c>
+      <c r="J42">
+        <v>0.9099999656677247</v>
+      </c>
+      <c r="K42">
+        <v>30</v>
+      </c>
+      <c r="L42">
+        <v>504.8999977111816</v>
+      </c>
+      <c r="M42">
+        <v>4.549999828338623</v>
+      </c>
+      <c r="N42">
+        <v>2.495454545454546</v>
+      </c>
+      <c r="O42">
+        <v>7.045454373793168</v>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Truist Financial Corp</t>
+          <t>Bank OZK</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>TFC</t>
-        </is>
-      </c>
-      <c r="C43">
-        <v>1.620909090909091</v>
+          <t>OZK</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>financials</t>
+        </is>
       </c>
       <c r="D43">
-        <v>17.83</v>
+        <v>1.082818181818182</v>
       </c>
       <c r="E43">
-        <v>47.02000045776367</v>
+        <v>11.911</v>
       </c>
       <c r="F43">
-        <v>50.95000076293945</v>
+        <v>52.59000015258789</v>
       </c>
       <c r="G43">
-        <v>3.930000305175781</v>
+        <v>48.5099983215332</v>
+      </c>
+      <c r="H43">
+        <v>-4.080001831054688</v>
+      </c>
+      <c r="I43">
+        <v>7.830998168945312</v>
+      </c>
+      <c r="J43">
+        <v>0.7830998168945312</v>
+      </c>
+      <c r="K43">
+        <v>11</v>
+      </c>
+      <c r="L43">
+        <v>533.6099815368652</v>
+      </c>
+      <c r="M43">
+        <v>3.915499084472656</v>
+      </c>
+      <c r="N43">
+        <v>5.414090909090909</v>
+      </c>
+      <c r="O43">
+        <v>9.329589993563566</v>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>T. Rowe Price Group Inc</t>
+          <t>Franklin Resources Inc</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>TROW</t>
-        </is>
-      </c>
-      <c r="C44">
-        <v>3.789090909090909</v>
+          <t>BEN</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>financials</t>
+        </is>
       </c>
       <c r="D44">
-        <v>41.68</v>
+        <v>1.26</v>
       </c>
       <c r="E44">
-        <v>75.26000213623047</v>
+        <v>13.86</v>
       </c>
       <c r="F44">
-        <v>100.2399978637695</v>
+        <v>39.58000183105469</v>
       </c>
       <c r="G44">
-        <v>24.97999572753906</v>
+        <v>26.81999969482422</v>
+      </c>
+      <c r="H44">
+        <v>-12.76000213623047</v>
+      </c>
+      <c r="I44">
+        <v>1.099997863769532</v>
+      </c>
+      <c r="J44">
+        <v>0.1099997863769532</v>
+      </c>
+      <c r="K44">
+        <v>19</v>
+      </c>
+      <c r="L44">
+        <v>509.5799942016602</v>
+      </c>
+      <c r="M44">
+        <v>0.5499989318847662</v>
+      </c>
+      <c r="N44">
+        <v>6.3</v>
+      </c>
+      <c r="O44">
+        <v>6.849998931884766</v>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>United Overseas Bank Ltd</t>
+          <t>Columbia Banking System Inc</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>UOVEY</t>
-        </is>
-      </c>
-      <c r="C45">
-        <v>1.8141</v>
+          <t>COLB</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>financials</t>
+        </is>
       </c>
       <c r="D45">
-        <v>18.141</v>
+        <v>1.171818181818182</v>
       </c>
       <c r="E45">
-        <v>28.13999938964844</v>
+        <v>12.89</v>
       </c>
       <c r="F45">
-        <v>57.79999923706055</v>
+        <v>44.68000030517578</v>
       </c>
       <c r="G45">
-        <v>29.65999984741211</v>
+        <v>29.64999961853027</v>
+      </c>
+      <c r="H45">
+        <v>-15.03000068664551</v>
+      </c>
+      <c r="I45">
+        <v>-2.140000686645507</v>
+      </c>
+      <c r="J45">
+        <v>-0.2140000686645507</v>
+      </c>
+      <c r="K45">
+        <v>17</v>
+      </c>
+      <c r="L45">
+        <v>504.0499935150146</v>
+      </c>
+      <c r="M45">
+        <v>-1.070000343322754</v>
+      </c>
+      <c r="N45">
+        <v>5.859090909090909</v>
+      </c>
+      <c r="O45">
+        <v>4.789090565768156</v>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>U.S. Bancorp</t>
+          <t>Lincoln National Corp</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>USB</t>
-        </is>
-      </c>
-      <c r="C46">
-        <v>1.516818181818182</v>
+          <t>LNC</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>financials</t>
+        </is>
       </c>
       <c r="D46">
-        <v>16.685</v>
+        <v>1.44</v>
       </c>
       <c r="E46">
-        <v>51.36999893188477</v>
+        <v>15.84</v>
       </c>
       <c r="F46">
-        <v>56.59999847412109</v>
+        <v>66.26999664306641</v>
       </c>
       <c r="G46">
-        <v>5.229999542236328</v>
+        <v>36.45999908447266</v>
+      </c>
+      <c r="H46">
+        <v>-29.80999755859375</v>
+      </c>
+      <c r="I46">
+        <v>-13.96999755859375</v>
+      </c>
+      <c r="J46">
+        <v>-1.396999755859375</v>
+      </c>
+      <c r="K46">
+        <v>14</v>
+      </c>
+      <c r="L46">
+        <v>510.4399871826172</v>
+      </c>
+      <c r="M46">
+        <v>-6.984998779296875</v>
+      </c>
+      <c r="N46">
+        <v>7.199999999999999</v>
+      </c>
+      <c r="O46">
+        <v>0.2150012207031242</v>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Woori Financial Group Inc</t>
+          <t>Blackstone Secured Lending Fund</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>WF</t>
-        </is>
-      </c>
-      <c r="C47">
-        <v>2.34775</v>
+          <t>BXSL</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>financials</t>
+        </is>
       </c>
       <c r="D47">
-        <v>9.391</v>
+        <v>2.218333333333333</v>
       </c>
       <c r="E47">
-        <v>32</v>
-      </c>
-      <c r="F47">
-        <v>71.79000091552734</v>
+        <v>13.31</v>
       </c>
       <c r="G47">
-        <v>39.79000091552734</v>
+        <v>23.71999931335449</v>
+      </c>
+      <c r="K47">
+        <v>22</v>
+      </c>
+      <c r="L47">
+        <v>521.8399848937988</v>
+      </c>
+      <c r="N47">
+        <v>11.09166666666667</v>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>TBD</t>
+        </is>
       </c>
     </row>
   </sheetData>
